--- a/output/pdf_financials_xlsx/PHRX.xlsx
+++ b/output/pdf_financials_xlsx/PHRX.xlsx
@@ -1988,13 +1988,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.894293</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.709771</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.290893</v>
       </c>
     </row>
     <row r="93">
@@ -3226,7 +3226,11 @@
           <t>Reserve for warrants (Note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3633,7 +3637,11 @@
           <t>Reserve for warrants (Note 12)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>0.894293</v>
       </c>

--- a/output/pdf_financials_xlsx/PHRX.xlsx
+++ b/output/pdf_financials_xlsx/PHRX.xlsx
@@ -1048,13 +1048,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.411122</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.07503799999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.017898</v>
       </c>
     </row>
     <row r="35">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.411122</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.07503799999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.017898</v>
       </c>
     </row>
     <row r="37">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.577068</v>
+        <v>0.165946</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.12409</v>
+        <v>0.049052</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.023244</v>
+        <v>0.005346</v>
       </c>
     </row>
     <row r="49">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PHRX.xlsx
+++ b/output/pdf_financials_xlsx/PHRX.xlsx
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.050244</v>
+        <v>0.026216</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0.050244</v>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.8229109999999999</v>
+        <v>-0.846939</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.382261</v>
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.026216</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.050244</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.050244</v>
       </c>
     </row>
     <row r="101">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -4300,7 +4300,11 @@
           <t>Additions to intangible assets (Note 4)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -5633,7 +5637,11 @@
           <t>Additions to intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -6790,7 +6798,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7663,7 +7671,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHRX.xlsx
+++ b/output/pdf_financials_xlsx/PHRX.xlsx
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.873155</v>
+        <v>0.137189</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.432505</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.010344</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.873155</v>
+        <v>0.137189</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.432505</v>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.846939</v>
+        <v>0.163405</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.382261</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>736.4613780988271</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.449573</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.37002</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0</v>
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.44858</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.237152</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.253498</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5325,7 +5325,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>-1.010344</v>
       </c>
@@ -5606,7 +5610,11 @@
           <t>Proceeds from disposals of investments (Note 6)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.253498</v>
       </c>
@@ -7223,7 +7231,11 @@
           <t>Deferred income tax recovery (Note 16) -</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
